--- a/data/AHLdelegacije - Copy 24.2..xlsx
+++ b/data/AHLdelegacije - Copy 24.2..xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881B9E6A-E1E6-4A3B-9B46-43A90C814FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BEB4A4-437B-460E-B4A8-13B67CDA54FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHL" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
     <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2845" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="455">
   <si>
     <t>sl</t>
   </si>
@@ -1966,7 +1967,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2339,247 +2342,247 @@
   <sheetData>
     <row r="1" spans="1:61" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
-        <f>COUNTIF(A4:A50,"&lt;&gt;")</f>
+        <f t="shared" ref="A1:AF1" si="0">COUNTIF(A4:A50,"&lt;&gt;")</f>
         <v>34</v>
       </c>
       <c r="B1">
-        <f>COUNTIF(B4:B50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C1">
-        <f>COUNTIF(C4:C50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="D1">
-        <f>COUNTIF(D4:D50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="E1">
-        <f>COUNTIF(E4:E50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="F1">
-        <f>COUNTIF(F4:F50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="G1">
-        <f>COUNTIF(G4:G50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="H1">
-        <f>COUNTIF(H4:H50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="I1">
-        <f>COUNTIF(I4:I50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="J1">
-        <f>COUNTIF(J4:J50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="K1">
-        <f>COUNTIF(K4:K50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="L1">
-        <f>COUNTIF(L4:L50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="M1">
-        <f>COUNTIF(M4:M50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="O1">
-        <f>COUNTIF(O4:O50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="P1">
-        <f>COUNTIF(P4:P50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="Q1">
-        <f>COUNTIF(Q4:Q50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S1">
-        <f>COUNTIF(S4:S50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="T1">
-        <f>COUNTIF(T4:T50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="U1">
-        <f>COUNTIF(U4:U50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="V1">
-        <f>COUNTIF(V4:V50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="W1">
-        <f>COUNTIF(W4:W50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="X1">
-        <f>COUNTIF(X4:X50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="Y1">
-        <f>COUNTIF(Y4:Y50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="Z1">
-        <f>COUNTIF(Z4:Z50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AA1">
-        <f>COUNTIF(AA4:AA50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AB1">
-        <f>COUNTIF(AB4:AB50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AC1">
-        <f>COUNTIF(AC4:AC50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AD1">
-        <f>COUNTIF(AD4:AD50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AE1">
-        <f>COUNTIF(AE4:AE50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AF1">
-        <f>COUNTIF(AF4:AF50,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG50,"&lt;&gt;")</f>
+        <f t="shared" ref="AG1:BI1" si="1">COUNTIF(AG4:AG50,"&lt;&gt;")</f>
         <v>19</v>
       </c>
       <c r="AH1">
-        <f>COUNTIF(AH4:AH50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AI1">
-        <f>COUNTIF(AI4:AI50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AK1">
-        <f>COUNTIF(AK4:AK50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AL1">
-        <f>COUNTIF(AL4:AL50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AM1">
-        <f>COUNTIF(AM4:AM50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AN1">
-        <f>COUNTIF(AN4:AN50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AO1">
-        <f>COUNTIF(AO4:AO50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AP1">
-        <f>COUNTIF(AP4:AP50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AQ1">
-        <f>COUNTIF(AQ4:AQ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AS1">
-        <f>COUNTIF(AS4:AS50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AT1">
-        <f>COUNTIF(AT4:AT50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AU1">
-        <f>COUNTIF(AU4:AU50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AV1">
-        <f>COUNTIF(AV4:AV50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="AW1">
-        <f>COUNTIF(AW4:AW50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="AX1">
-        <f>COUNTIF(AX4:AX50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="AZ1">
-        <f>COUNTIF(AZ4:AZ50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="BA1">
-        <f>COUNTIF(BA4:BA50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="BB1">
-        <f>COUNTIF(BB4:BB50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="BC1">
-        <f>COUNTIF(BC4:BC50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="BD1">
-        <f>COUNTIF(BD4:BD50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="BE1">
-        <f>COUNTIF(BE4:BE50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="BF1">
-        <f>COUNTIF(BF4:BF50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BH1">
-        <f>COUNTIF(BH4:BH50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BI1">
-        <f>COUNTIF(BI4:BI50,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3471,7 +3474,7 @@
       <c r="BA6" t="s">
         <v>90</v>
       </c>
-      <c r="BB6" s="67" t="s">
+      <c r="BB6" t="s">
         <v>93</v>
       </c>
       <c r="BC6" s="4" t="s">
@@ -3480,7 +3483,7 @@
       <c r="BD6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="BE6" s="67" t="s">
+      <c r="BE6" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3641,7 +3644,7 @@
       <c r="AZ7" t="s">
         <v>99</v>
       </c>
-      <c r="BA7" s="67" t="s">
+      <c r="BA7" t="s">
         <v>93</v>
       </c>
       <c r="BB7" t="s">
@@ -3799,10 +3802,10 @@
       <c r="AX8" t="s">
         <v>101</v>
       </c>
-      <c r="AY8" s="67" t="s">
+      <c r="AY8" t="s">
         <v>106</v>
       </c>
-      <c r="AZ8" s="67" t="s">
+      <c r="AZ8" t="s">
         <v>106</v>
       </c>
       <c r="BA8" t="s">
@@ -4113,10 +4116,10 @@
       <c r="AV10" t="s">
         <v>105</v>
       </c>
-      <c r="AW10" s="67" t="s">
+      <c r="AW10" t="s">
         <v>115</v>
       </c>
-      <c r="AX10" s="67" t="s">
+      <c r="AX10" t="s">
         <v>122</v>
       </c>
       <c r="AY10" t="s">
@@ -4571,7 +4574,7 @@
       <c r="AU13" t="s">
         <v>105</v>
       </c>
-      <c r="AV13" s="67" t="s">
+      <c r="AV13" t="s">
         <v>93</v>
       </c>
       <c r="AW13" t="s">
@@ -4711,13 +4714,13 @@
       <c r="AR14" t="s">
         <v>122</v>
       </c>
-      <c r="AS14" s="67" t="s">
+      <c r="AS14" t="s">
         <v>106</v>
       </c>
       <c r="AT14" t="s">
         <v>136</v>
       </c>
-      <c r="AU14" s="67" t="s">
+      <c r="AU14" t="s">
         <v>115</v>
       </c>
       <c r="AY14" s="4"/>
@@ -4840,7 +4843,7 @@
       <c r="AM15" t="s">
         <v>121</v>
       </c>
-      <c r="AN15" s="67" t="s">
+      <c r="AN15" t="s">
         <v>115</v>
       </c>
       <c r="AO15" t="s">
@@ -4849,7 +4852,7 @@
       <c r="AP15" t="s">
         <v>128</v>
       </c>
-      <c r="AQ15" s="67" t="s">
+      <c r="AQ15" t="s">
         <v>122</v>
       </c>
       <c r="AR15" t="s">
@@ -4988,7 +4991,7 @@
       <c r="AN16" t="s">
         <v>116</v>
       </c>
-      <c r="AO16" s="67" t="s">
+      <c r="AO16" t="s">
         <v>106</v>
       </c>
       <c r="AP16" t="s">
@@ -4997,13 +5000,13 @@
       <c r="AQ16" t="s">
         <v>111</v>
       </c>
-      <c r="AR16" s="67" t="s">
+      <c r="AR16" t="s">
         <v>115</v>
       </c>
       <c r="AS16" t="s">
         <v>80</v>
       </c>
-      <c r="AT16" s="67" t="s">
+      <c r="AT16" t="s">
         <v>106</v>
       </c>
       <c r="AU16" t="s">
@@ -5126,7 +5129,7 @@
       <c r="AL17" t="s">
         <v>93</v>
       </c>
-      <c r="AM17" s="67" t="s">
+      <c r="AM17" t="s">
         <v>115</v>
       </c>
       <c r="AN17" t="s">
@@ -5135,7 +5138,7 @@
       <c r="AO17" t="s">
         <v>129</v>
       </c>
-      <c r="AP17" s="67" t="s">
+      <c r="AP17" t="s">
         <v>110</v>
       </c>
       <c r="AQ17" t="s">
@@ -5260,13 +5263,13 @@
       <c r="AI18" t="s">
         <v>135</v>
       </c>
-      <c r="AJ18" s="67" t="s">
+      <c r="AJ18" t="s">
         <v>143</v>
       </c>
-      <c r="AK18" s="67" t="s">
+      <c r="AK18" t="s">
         <v>106</v>
       </c>
-      <c r="AL18" s="67" t="s">
+      <c r="AL18" t="s">
         <v>122</v>
       </c>
       <c r="AM18" t="s">
@@ -5377,10 +5380,10 @@
       <c r="AE19" t="s">
         <v>101</v>
       </c>
-      <c r="AF19" s="67" t="s">
+      <c r="AF19" t="s">
         <v>122</v>
       </c>
-      <c r="AG19" s="67" t="s">
+      <c r="AG19" t="s">
         <v>122</v>
       </c>
       <c r="AH19" t="s">
@@ -5484,7 +5487,7 @@
       <c r="Z20" t="s">
         <v>135</v>
       </c>
-      <c r="AA20" s="67" t="s">
+      <c r="AA20" t="s">
         <v>101</v>
       </c>
       <c r="AB20" t="s">
@@ -5505,10 +5508,10 @@
       <c r="AG20" t="s">
         <v>111</v>
       </c>
-      <c r="AH20" s="67" t="s">
+      <c r="AH20" t="s">
         <v>144</v>
       </c>
-      <c r="AI20" s="67" t="s">
+      <c r="AI20" t="s">
         <v>106</v>
       </c>
       <c r="AJ20" t="s">
@@ -5600,7 +5603,7 @@
       <c r="Y21" t="s">
         <v>93</v>
       </c>
-      <c r="Z21" s="67" t="s">
+      <c r="Z21" t="s">
         <v>106</v>
       </c>
       <c r="AA21" t="s">
@@ -5615,7 +5618,7 @@
       <c r="AD21" t="s">
         <v>115</v>
       </c>
-      <c r="AE21" s="67" t="s">
+      <c r="AE21" t="s">
         <v>106</v>
       </c>
       <c r="AF21" t="s">
@@ -5693,10 +5696,10 @@
       <c r="Q22" t="s">
         <v>135</v>
       </c>
-      <c r="R22" s="67" t="s">
+      <c r="R22" t="s">
         <v>147</v>
       </c>
-      <c r="S22" s="67" t="s">
+      <c r="S22" t="s">
         <v>100</v>
       </c>
       <c r="T22" t="s">
@@ -5705,7 +5708,7 @@
       <c r="U22" t="s">
         <v>122</v>
       </c>
-      <c r="V22" s="67" t="s">
+      <c r="V22" t="s">
         <v>93</v>
       </c>
       <c r="W22" t="s">
@@ -5714,7 +5717,7 @@
       <c r="X22" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="Y22" s="67" t="s">
+      <c r="Y22" t="s">
         <v>106</v>
       </c>
       <c r="Z22" t="s">
@@ -5723,13 +5726,13 @@
       <c r="AA22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AB22" s="67" t="s">
+      <c r="AB22" t="s">
         <v>101</v>
       </c>
       <c r="AC22" t="s">
         <v>115</v>
       </c>
-      <c r="AD22" s="67" t="s">
+      <c r="AD22" t="s">
         <v>106</v>
       </c>
       <c r="AE22" t="s">
@@ -5792,16 +5795,16 @@
       <c r="M23" t="s">
         <v>106</v>
       </c>
-      <c r="N23" s="67" t="s">
+      <c r="N23" t="s">
         <v>93</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="P23" s="67" t="s">
+      <c r="P23" t="s">
         <v>122</v>
       </c>
-      <c r="Q23" s="67" t="s">
+      <c r="Q23" t="s">
         <v>115</v>
       </c>
       <c r="R23" s="4" t="s">
@@ -5813,13 +5816,13 @@
       <c r="T23" t="s">
         <v>115</v>
       </c>
-      <c r="U23" s="67" t="s">
+      <c r="U23" t="s">
         <v>137</v>
       </c>
       <c r="V23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W23" s="67" t="s">
+      <c r="W23" t="s">
         <v>122</v>
       </c>
       <c r="X23" t="s">
@@ -5837,7 +5840,7 @@
       <c r="AB23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="AC23" s="67" t="s">
+      <c r="AC23" t="s">
         <v>122</v>
       </c>
       <c r="AD23" t="s">
@@ -5888,7 +5891,7 @@
       <c r="L24" t="s">
         <v>115</v>
       </c>
-      <c r="M24" s="67" t="s">
+      <c r="M24" t="s">
         <v>122</v>
       </c>
       <c r="N24" t="s">
@@ -5909,7 +5912,7 @@
       <c r="S24" t="s">
         <v>107</v>
       </c>
-      <c r="T24" s="67" t="s">
+      <c r="T24" t="s">
         <v>106</v>
       </c>
       <c r="U24" t="s">
@@ -5978,7 +5981,7 @@
       <c r="J25" t="s">
         <v>122</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" t="s">
         <v>122</v>
       </c>
       <c r="L25" t="s">
@@ -6056,13 +6059,13 @@
       <c r="F26" t="s">
         <v>135</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" t="s">
         <v>125</v>
       </c>
       <c r="H26" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="67" t="s">
+      <c r="I26" t="s">
         <v>106</v>
       </c>
       <c r="J26" t="s">
@@ -6071,7 +6074,7 @@
       <c r="K26" t="s">
         <v>129</v>
       </c>
-      <c r="L26" s="67" t="s">
+      <c r="L26" t="s">
         <v>122</v>
       </c>
       <c r="M26" s="4" t="s">
@@ -6122,7 +6125,7 @@
       <c r="D27" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="67" t="s">
+      <c r="E27" t="s">
         <v>122</v>
       </c>
       <c r="F27" t="s">
@@ -6131,13 +6134,13 @@
       <c r="G27" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="67" t="s">
+      <c r="H27" t="s">
         <v>137</v>
       </c>
       <c r="I27" t="s">
         <v>129</v>
       </c>
-      <c r="J27" s="67" t="s">
+      <c r="J27" t="s">
         <v>125</v>
       </c>
       <c r="K27" t="s">
@@ -6189,7 +6192,7 @@
       <c r="E28" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="67" t="s">
+      <c r="F28" t="s">
         <v>101</v>
       </c>
       <c r="G28" t="s">
@@ -6222,7 +6225,7 @@
       <c r="AM28" s="4"/>
     </row>
     <row r="29" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
+      <c r="A29" t="s">
         <v>106</v>
       </c>
       <c r="B29" t="s">
@@ -6231,7 +6234,7 @@
       <c r="C29" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" t="s">
         <v>99</v>
       </c>
       <c r="E29" t="s">
@@ -6268,7 +6271,7 @@
       <c r="B30" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="67" t="s">
+      <c r="C30" t="s">
         <v>106</v>
       </c>
       <c r="D30" t="s">
@@ -6301,7 +6304,7 @@
       <c r="A31" t="s">
         <v>129</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" t="s">
         <v>122</v>
       </c>
       <c r="C31" t="s">
@@ -11878,4 +11881,689 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A9813D-578C-4013-A50A-8663E035A45A}">
+  <dimension ref="AH1:AJ61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="35" max="35" width="15.42578125" customWidth="1"/>
+    <col min="36" max="36" width="9.140625" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="34:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ1" s="67">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="34:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ2" s="67">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="34:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ3" s="67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ4" s="67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AJ5" s="67">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ6" s="67">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ7" s="67">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ8" s="67">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ9" s="67">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ10" s="67">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ11" s="67">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ12" s="67">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ13" s="67">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ14" s="67">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ15" s="67">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ16" s="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ17" s="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ18" s="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ19" s="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ20" s="67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ22" s="67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ23" s="67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ25" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ26" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ27" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ28" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ29" s="67">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ30" s="67">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ31" s="67">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ32" s="67">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ33" s="67">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ34" s="67">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ35" s="67">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ36" s="67">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ37" s="67">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ38" s="67">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ39" s="67">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ40" s="67">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ41" s="67">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ42" s="67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ43" s="67">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ44" s="67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ45" s="67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ46" s="67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ47" s="67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ49" s="67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ50" s="67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ51" s="67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ52" s="67">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH53" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ53" s="67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ54" s="67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ55" s="67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ56" s="67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ57" s="67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ58" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ59" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ60" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ61" s="67">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>